--- a/Data/EXCEL/Transfer/dividend/20260215_1_2/3149-dividend-20260215_1_2.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260215_1_2/3149-dividend-20260215_1_2.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\dividend\20260215_1_2(所屬年度_現金殖利率＋股票殖利率)\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260215_1_2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{949C6F12-070F-4FD7-ADFD-F4A421884D0F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{8254387E-BC18-491C-A280-FA32F47D6EAF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9720" yWindow="2670" windowWidth="21285" windowHeight="16275" xr2:uid="{8478F7A4-BDAC-4D39-9273-640F30178E0C}"/>
+    <workbookView xWindow="3492" yWindow="1344" windowWidth="16656" windowHeight="10992" xr2:uid="{B1D5405B-3138-49FC-AA91-396F21DFA297}"/>
   </bookViews>
   <sheets>
     <sheet name="3149-dividend-20260215_1_2" sheetId="1" r:id="rId1"/>
@@ -1448,30 +1448,30 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59D9C035-D6A2-4448-BDE5-02E7641527A3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1C5AB81B-AE98-4082-8776-DB1DDA96DE70}">
   <dimension ref="A1:X45"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.375" customWidth="1"/>
-    <col min="2" max="2" width="4.875" customWidth="1"/>
-    <col min="3" max="3" width="11" customWidth="1"/>
-    <col min="4" max="4" width="7.125" customWidth="1"/>
-    <col min="5" max="5" width="6.75" customWidth="1"/>
-    <col min="6" max="7" width="7.125" customWidth="1"/>
-    <col min="8" max="8" width="6.75" customWidth="1"/>
-    <col min="9" max="10" width="7.125" customWidth="1"/>
-    <col min="11" max="13" width="6.75" customWidth="1"/>
-    <col min="14" max="15" width="7.125" customWidth="1"/>
-    <col min="16" max="18" width="6.75" customWidth="1"/>
-    <col min="19" max="19" width="7.125" customWidth="1"/>
-    <col min="20" max="20" width="6.75" customWidth="1"/>
-    <col min="21" max="21" width="7.125" customWidth="1"/>
-    <col min="22" max="22" width="6.75" customWidth="1"/>
-    <col min="23" max="23" width="7.125" customWidth="1"/>
-    <col min="24" max="24" width="8.5" customWidth="1"/>
+    <col min="1" max="1" width="3.77734375" customWidth="1"/>
+    <col min="2" max="2" width="4.21875" customWidth="1"/>
+    <col min="3" max="3" width="9.6640625" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" customWidth="1"/>
+    <col min="5" max="5" width="5.88671875" customWidth="1"/>
+    <col min="6" max="7" width="6.109375" customWidth="1"/>
+    <col min="8" max="8" width="5.88671875" customWidth="1"/>
+    <col min="9" max="10" width="6.109375" customWidth="1"/>
+    <col min="11" max="13" width="5.88671875" customWidth="1"/>
+    <col min="14" max="15" width="6.109375" customWidth="1"/>
+    <col min="16" max="18" width="5.88671875" customWidth="1"/>
+    <col min="19" max="19" width="6.109375" customWidth="1"/>
+    <col min="20" max="20" width="5.88671875" customWidth="1"/>
+    <col min="21" max="21" width="6.109375" customWidth="1"/>
+    <col min="22" max="22" width="5.88671875" customWidth="1"/>
+    <col min="23" max="23" width="6.109375" customWidth="1"/>
+    <col min="24" max="24" width="6.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:24" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:24" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A1" s="19" t="s">
         <v>0</v>
       </c>
@@ -1505,7 +1505,7 @@
       <c r="W1" s="28"/>
       <c r="X1" s="20"/>
     </row>
-    <row r="2" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
@@ -1541,7 +1541,7 @@
       <c r="W2" s="30"/>
       <c r="X2" s="31"/>
     </row>
-    <row r="3" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A3" s="21" t="s">
         <v>2</v>
       </c>
@@ -1593,7 +1593,7 @@
       </c>
       <c r="X3" s="34"/>
     </row>
-    <row r="4" spans="1:24" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:24" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A4" s="23"/>
       <c r="B4" s="24"/>
       <c r="C4" s="7"/>
@@ -1661,7 +1661,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A5" s="35">
         <v>2025</v>
       </c>
@@ -1733,7 +1733,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A6" s="11" t="s">
         <v>29</v>
       </c>
@@ -1807,7 +1807,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A7" s="37">
         <v>2024</v>
       </c>
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A8" s="16" t="s">
         <v>29</v>
       </c>
@@ -1953,7 +1953,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
         <v>29</v>
       </c>
@@ -2027,7 +2027,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A10" s="35">
         <v>2023</v>
       </c>
@@ -2099,7 +2099,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>29</v>
       </c>
@@ -2173,7 +2173,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A12" s="11" t="s">
         <v>29</v>
       </c>
@@ -2247,7 +2247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A13" s="37">
         <v>2022</v>
       </c>
@@ -2319,7 +2319,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A14" s="16" t="s">
         <v>29</v>
       </c>
@@ -2393,7 +2393,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A15" s="16" t="s">
         <v>29</v>
       </c>
@@ -2467,7 +2467,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A16" s="35">
         <v>2021</v>
       </c>
@@ -2539,7 +2539,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A17" s="11" t="s">
         <v>29</v>
       </c>
@@ -2613,7 +2613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A18" s="11" t="s">
         <v>29</v>
       </c>
@@ -2687,7 +2687,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A19" s="37">
         <v>2020</v>
       </c>
@@ -2759,7 +2759,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A20" s="16" t="s">
         <v>29</v>
       </c>
@@ -2833,7 +2833,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A21" s="16" t="s">
         <v>29</v>
       </c>
@@ -2907,7 +2907,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A22" s="35">
         <v>2019</v>
       </c>
@@ -2979,7 +2979,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A23" s="11" t="s">
         <v>29</v>
       </c>
@@ -3053,7 +3053,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A24" s="11" t="s">
         <v>29</v>
       </c>
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A25" s="37">
         <v>2018</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A26" s="35">
         <v>2017</v>
       </c>
@@ -3271,7 +3271,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A27" s="37">
         <v>2016</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A28" s="35">
         <v>2015</v>
       </c>
@@ -3415,7 +3415,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A29" s="37">
         <v>2014</v>
       </c>
@@ -3487,7 +3487,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A30" s="35">
         <v>2013</v>
       </c>
@@ -3559,7 +3559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A31" s="37">
         <v>2012</v>
       </c>
@@ -3631,7 +3631,7 @@
         <v>3.51</v>
       </c>
     </row>
-    <row r="32" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A32" s="35">
         <v>2011</v>
       </c>
@@ -3703,7 +3703,7 @@
         <v>2.93</v>
       </c>
     </row>
-    <row r="33" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A33" s="37">
         <v>2010</v>
       </c>
@@ -3775,7 +3775,7 @@
         <v>0.37</v>
       </c>
     </row>
-    <row r="34" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A34" s="35">
         <v>2009</v>
       </c>
@@ -3847,7 +3847,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A35" s="37">
         <v>2008</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A36" s="35">
         <v>2007</v>
       </c>
@@ -3991,7 +3991,7 @@
         <v>5.09</v>
       </c>
     </row>
-    <row r="37" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A37" s="37">
         <v>2006</v>
       </c>
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A38" s="35">
         <v>2005</v>
       </c>
@@ -4135,7 +4135,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="39" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A39" s="37">
         <v>2004</v>
       </c>
@@ -4207,7 +4207,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="40" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A40" s="35">
         <v>2003</v>
       </c>
@@ -4279,7 +4279,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="41" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A41" s="37">
         <v>2002</v>
       </c>
@@ -4351,7 +4351,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="42" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A42" s="35">
         <v>2000</v>
       </c>
@@ -4423,7 +4423,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="43" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A43" s="37">
         <v>1999</v>
       </c>
@@ -4495,7 +4495,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="44" spans="1:24" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:24" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A44" s="35">
         <v>1998</v>
       </c>
@@ -4567,7 +4567,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="45" spans="1:24" s="14" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:24" s="14" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
       <c r="A45" s="37" t="s">
         <v>37</v>
       </c>
